--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_28-09-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_28-09-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Core-Products_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D29852-A98E-4206-B7D4-C7774E8A3C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="2130" yWindow="2160" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="339">
   <si>
     <t>SKU</t>
   </si>
@@ -445,120 +451,9 @@
     <t>£19.48</t>
   </si>
   <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-combi-loft-roll-100mm-thick-1389m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-combi-loft-roll-150mm-thick-918m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-loft-roll-insulation-44-earthwool-combi-cut-170mm-801m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-loft-roll-44-200mm-insulation-684m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-acoustic-roll-25mm-insulation-apr---2664m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-acoustic-roll-50mm-insulation-apr---162m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-acoustic-roll-75mm-insulation-apr---174m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-acoustic-roll-100mm-insulation-apr---1236m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-dritherm-32-100mm-cavity-wall-slab---3276m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-dritherm-32-150mm-cavity-wall-slab---218m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-dritherm-37-75mm-cavity-wall-slab---437m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-dritherm-37-100mm-cavity-wall-slab---655m2.html</t>
-  </si>
-  <si>
     <t>N/L</t>
   </si>
   <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-rwa45-acoustic-insulation-slab-25mm-138-24m2-pallet.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-rwa45-acoustic-insulation-slab-50mm-6-48m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-rwa45-acoustic-insulation-slab-75mm-432m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-rwa45-acoustic-insulation-slab-100mm-2-88m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-flexi-slab-acoustic-insulation-1-2m-x-600mm-x-50mm-8-64m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-flexi-slab-acoustic-insulation-1-2m-x-600mm-x-100mm-4-32m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-flexi-slab-acoustic-insulation-1-2m-x-600mm-x-140mm-2-88m2.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-flexi-slab-acoustic-insulation-100-x-1200-x-400mm-6-slabs-per-288m2-pk.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rockwool-flexi-slab-acoustic-insulation-1200mm-x-400mm-x-140mm-4608m2-pallet.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/rw3-acoustic-slab-insulation-100mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/tf70-floor-insulation-board-kingspan-thermafloor-50mm-11-52m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/kingspan-thermafloor-tf7075-75mm-floor-insulation-board-1152m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/tf70-floor-insulation-board-kingspan-thermafloor-100mm-864m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/kingspan-thermaroof-tr27-pir-flat-roof-insulation-board-1200-x-1200-x-100mm---pack-of-4-sheets.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/kingspan-thermaroof-tr27-pir-flat-roof-insulation-board-1200-x-1200-x-150mm---pack-of-2-sheets.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/cavity-board-by-kingspan-k106-kooltherm-90mm-2-16m2-pack.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-plasterboard-tapered-edge-wallboard-2400-x-1200-x-12-5mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/knauf-drywall-plasterboard-adhesive-25kg.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/british-gypsum-thistle-multifinish-plaster-25kg.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-fire-plasterboard-2400mm-x-1200mm-x-15mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-fire-plasterboard-2400mm-x-1200mm-x-12-5mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-aqua-moisture-resistant-plasterboard-2-4m-x-1-2m-x-12-5mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-standard-plasterboard-2400mm-x-1200mm-x-12-5mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-acoustic-plasterboard-2400mm-x-1200mm-x-12-5mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/gypfor-acoustic-plasterboard-2400mm-x-1200mm-x-15mm.html</t>
-  </si>
-  <si>
     <t>£34.99</t>
   </si>
   <si>
@@ -1079,13 +974,76 @@
   </si>
   <si>
     <t>£11.38</t>
+  </si>
+  <si>
+    <t>£33.00</t>
+  </si>
+  <si>
+    <t>£45.00</t>
+  </si>
+  <si>
+    <t>£80.00</t>
+  </si>
+  <si>
+    <t>£70.00</t>
+  </si>
+  <si>
+    <t>£35.00</t>
+  </si>
+  <si>
+    <t>£13.34</t>
+  </si>
+  <si>
+    <t>£28.75</t>
+  </si>
+  <si>
+    <t>£29.50</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£47.50</t>
+  </si>
+  <si>
+    <t>£43.50</t>
+  </si>
+  <si>
+    <t>£665.00</t>
+  </si>
+  <si>
+    <t>£495.00</t>
+  </si>
+  <si>
+    <t>£260.00</t>
+  </si>
+  <si>
+    <t>£237.50</t>
+  </si>
+  <si>
+    <t>£235.00</t>
+  </si>
+  <si>
+    <t>£210.00</t>
+  </si>
+  <si>
+    <t>£150.00</t>
+  </si>
+  <si>
+    <t>£94.92</t>
+  </si>
+  <si>
+    <t>£10.75</t>
+  </si>
+  <si>
+    <t>£11.50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1148,13 +1106,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1192,7 +1158,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1226,6 +1192,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1260,9 +1227,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1435,11 +1403,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,7 +1439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1482,28 +1450,28 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>143</v>
+        <v>318</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="G2" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="H2" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="I2" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="J2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1514,28 +1482,28 @@
         <v>100</v>
       </c>
       <c r="D3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" t="s">
         <v>144</v>
       </c>
-      <c r="E3" t="s">
-        <v>181</v>
-      </c>
       <c r="F3" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="G3" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="H3" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="I3" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="J3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1546,28 +1514,28 @@
         <v>101</v>
       </c>
       <c r="D4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E4" t="s">
         <v>145</v>
       </c>
-      <c r="E4" t="s">
-        <v>182</v>
-      </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="G4" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="I4" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="J4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1578,28 +1546,28 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>318</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="G5" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="H5" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="I5" t="s">
-        <v>302</v>
+        <v>265</v>
       </c>
       <c r="J5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1610,28 +1578,28 @@
         <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>319</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="G6" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="H6" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="I6" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="J6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1642,28 +1610,28 @@
         <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>319</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="F7" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="G7" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="H7" t="s">
-        <v>271</v>
+        <v>234</v>
       </c>
       <c r="I7" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="J7" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1674,28 +1642,28 @@
         <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>320</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>147</v>
       </c>
       <c r="F8" t="s">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="H8" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="I8" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="J8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1706,28 +1674,28 @@
         <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>321</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="F9" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="G9" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="H9" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="I9" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="J9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1738,28 +1706,28 @@
         <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="F10" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="G10" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="H10" t="s">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="I10" t="s">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="J10" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1770,28 +1738,28 @@
         <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>322</v>
       </c>
       <c r="E11" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="G11" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H11" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="I11" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="J11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1802,28 +1770,28 @@
         <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>323</v>
       </c>
       <c r="E12" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="F12" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="G12" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="H12" t="s">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="I12" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="J12" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1834,28 +1802,28 @@
         <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>323</v>
       </c>
       <c r="E13" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="F13" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="G13" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="H13" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="I13" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="J13" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1866,28 +1834,28 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E14" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="F14" t="s">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="G14" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="H14" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="I14" t="s">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="J14" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1898,28 +1866,28 @@
         <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>324</v>
       </c>
       <c r="E15" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="F15" t="s">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="G15" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="H15" t="s">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="I15" t="s">
-        <v>311</v>
+        <v>274</v>
       </c>
       <c r="J15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1930,28 +1898,28 @@
         <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>325</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="F16" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="G16" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="H16" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="I16" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="J16" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1962,28 +1930,28 @@
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>325</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="F17" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="G17" t="s">
-        <v>252</v>
+        <v>215</v>
       </c>
       <c r="H17" t="s">
         <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="J17" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1994,28 +1962,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>326</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>156</v>
       </c>
       <c r="F18" t="s">
-        <v>221</v>
+        <v>184</v>
       </c>
       <c r="G18" t="s">
-        <v>253</v>
+        <v>216</v>
       </c>
       <c r="H18" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="I18" t="s">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="J18" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2026,28 +1994,28 @@
         <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>327</v>
       </c>
       <c r="E19" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="F19" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="G19" t="s">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="H19" t="s">
-        <v>282</v>
+        <v>245</v>
       </c>
       <c r="I19" t="s">
         <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2058,28 +2026,28 @@
         <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>327</v>
       </c>
       <c r="E20" t="s">
-        <v>195</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="G20" t="s">
-        <v>255</v>
+        <v>218</v>
       </c>
       <c r="H20" t="s">
-        <v>283</v>
+        <v>246</v>
       </c>
       <c r="I20" t="s">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="J20" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2090,28 +2058,28 @@
         <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>328</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>159</v>
       </c>
       <c r="F21" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="G21" t="s">
-        <v>256</v>
+        <v>219</v>
       </c>
       <c r="H21" t="s">
-        <v>284</v>
+        <v>247</v>
       </c>
       <c r="I21" t="s">
-        <v>315</v>
+        <v>278</v>
       </c>
       <c r="J21" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2122,28 +2090,28 @@
         <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>163</v>
+        <v>322</v>
       </c>
       <c r="E22" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>257</v>
+        <v>220</v>
       </c>
       <c r="H22" t="s">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J22" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2154,28 +2122,28 @@
         <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="F23" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G23" t="s">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="H23" t="s">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="I23" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J23" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2186,28 +2154,28 @@
         <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="E24" t="s">
-        <v>199</v>
+        <v>162</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G24" t="s">
-        <v>259</v>
+        <v>222</v>
       </c>
       <c r="H24" t="s">
-        <v>287</v>
+        <v>250</v>
       </c>
       <c r="I24" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J24" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2218,28 +2186,28 @@
         <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="F25" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="G25" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="H25" t="s">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="I25" t="s">
-        <v>316</v>
+        <v>279</v>
       </c>
       <c r="J25" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2250,28 +2218,28 @@
         <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E26" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="F26" t="s">
-        <v>225</v>
+        <v>188</v>
       </c>
       <c r="G26" t="s">
-        <v>261</v>
+        <v>224</v>
       </c>
       <c r="H26" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
       <c r="I26" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="J26" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2282,28 +2250,28 @@
         <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="E27" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="F27" t="s">
-        <v>226</v>
+        <v>189</v>
       </c>
       <c r="G27" t="s">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="H27" t="s">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="I27" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="J27" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2314,28 +2282,28 @@
         <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="F28" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="G28" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="H28" t="s">
-        <v>291</v>
+        <v>254</v>
       </c>
       <c r="I28" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="J28" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2346,28 +2314,28 @@
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>166</v>
+        <v>331</v>
       </c>
       <c r="E29" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="G29" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="I29" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="J29" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2378,28 +2346,28 @@
         <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>167</v>
+        <v>332</v>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F30" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="G30" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H30" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="I30" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="J30" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2410,28 +2378,28 @@
         <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>333</v>
       </c>
       <c r="E31" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="G31" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H31" t="s">
-        <v>294</v>
+        <v>257</v>
       </c>
       <c r="I31" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="J31" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2442,28 +2410,28 @@
         <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>331</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F32" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="G32" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H32" t="s">
-        <v>295</v>
+        <v>258</v>
       </c>
       <c r="I32" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="J32" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2474,28 +2442,28 @@
         <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>334</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="F33" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="G33" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="H33" t="s">
-        <v>296</v>
+        <v>259</v>
       </c>
       <c r="I33" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="J33" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2506,28 +2474,28 @@
         <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>170</v>
+        <v>335</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="F34" t="s">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="G34" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="I34" t="s">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="J34" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2538,28 +2506,28 @@
         <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>336</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="F35" t="s">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="G35" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
       <c r="H35" t="s">
-        <v>298</v>
+        <v>261</v>
       </c>
       <c r="I35" t="s">
-        <v>322</v>
+        <v>285</v>
       </c>
       <c r="J35" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2570,28 +2538,28 @@
         <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="G36" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H36" t="s">
-        <v>299</v>
+        <v>262</v>
       </c>
       <c r="I36" t="s">
-        <v>323</v>
+        <v>286</v>
       </c>
       <c r="J36" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2602,28 +2570,28 @@
         <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="F37" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="G37" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="H37" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="I37" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="J37" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2634,28 +2602,28 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>337</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>237</v>
+        <v>200</v>
       </c>
       <c r="G38" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="H38" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="I38" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="J38" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2666,28 +2634,28 @@
         <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>338</v>
       </c>
       <c r="E39" t="s">
-        <v>208</v>
+        <v>171</v>
       </c>
       <c r="F39" t="s">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="G39" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="H39" t="s">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="I39" t="s">
-        <v>325</v>
+        <v>288</v>
       </c>
       <c r="J39" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2698,28 +2666,28 @@
         <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I40" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J40" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2730,28 +2698,28 @@
         <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F41" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G41" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H41" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I41" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J41" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2762,28 +2730,28 @@
         <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H42" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I42" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J42" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2794,28 +2762,28 @@
         <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J43" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2826,28 +2794,28 @@
         <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I44" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J44" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2858,28 +2826,28 @@
         <v>141</v>
       </c>
       <c r="D45" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="E45" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H45" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I45" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J45" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2890,25 +2858,25 @@
         <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="E46" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G46" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="H46" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="I46" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J46" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
